--- a/data/trans_dic/Q45B_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/Q45B_R-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas</t>
+          <t>Población que han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,26</t>
+          <t>0,0; 1,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,59</t>
+          <t>0,74; 2,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,46</t>
+          <t>0,73; 2,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,48; 6,81</t>
+          <t>3,43; 6,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,12; 5,08</t>
+          <t>2,24; 5,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,12; 4,75</t>
+          <t>2,17; 4,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,9; 3,53</t>
+          <t>1,84; 3,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,71; 3,53</t>
+          <t>1,67; 3,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,64; 3,26</t>
+          <t>1,65; 3,18</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,86</t>
+          <t>0,94; 2,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,56</t>
+          <t>0,9; 2,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,39</t>
+          <t>0,29; 1,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,91; 10,44</t>
+          <t>7,07; 10,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,91; 8,98</t>
+          <t>5,85; 9,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,69; 4,9</t>
+          <t>2,64; 4,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,19; 6,38</t>
+          <t>4,24; 6,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,53; 5,52</t>
+          <t>3,65; 5,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,88</t>
+          <t>1,62; 2,89</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,49</t>
+          <t>1,07; 3,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,28; 5,19</t>
+          <t>2,29; 5,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,4</t>
+          <t>0,17; 1,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,23; 7,77</t>
+          <t>4,23; 7,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,34; 9,17</t>
+          <t>5,53; 9,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,55</t>
+          <t>1,98; 4,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,96; 5,07</t>
+          <t>3,0; 5,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,15; 6,71</t>
+          <t>4,24; 6,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,6</t>
+          <t>1,33; 2,62</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,56; 5,03</t>
+          <t>2,54; 4,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,52; 5,05</t>
+          <t>2,54; 4,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,95</t>
+          <t>0,61; 1,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,44; 12,38</t>
+          <t>8,38; 12,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,65; 12,26</t>
+          <t>8,46; 12,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,75; 5,23</t>
+          <t>2,8; 5,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,97; 8,27</t>
+          <t>6,09; 8,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,96; 8,25</t>
+          <t>5,93; 8,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,89; 3,32</t>
+          <t>1,94; 3,47</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,53</t>
+          <t>1,52; 2,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,99; 3,12</t>
+          <t>1,98; 3,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,37</t>
+          <t>0,67; 1,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,92; 8,74</t>
+          <t>6,95; 8,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,52; 8,4</t>
+          <t>6,52; 8,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,94; 4,13</t>
+          <t>2,98; 4,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,39; 5,53</t>
+          <t>4,44; 5,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,53; 5,59</t>
+          <t>4,49; 5,58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,93; 2,65</t>
+          <t>1,95; 2,64</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas</t>
+          <t>Población que han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 8712</t>
+          <t>0; 9423</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4828; 18171</t>
+          <t>5175; 17806</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4917; 16604</t>
+          <t>4932; 17084</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23923; 46853</t>
+          <t>23598; 45278</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14749; 35356</t>
+          <t>15572; 35281</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14155; 31785</t>
+          <t>14555; 31476</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26294; 48766</t>
+          <t>25417; 47655</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>23861; 49320</t>
+          <t>23338; 47135</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>22029; 43876</t>
+          <t>22122; 42708</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9371; 27467</t>
+          <t>9004; 25901</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9381; 25918</t>
+          <t>9122; 25965</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2988; 14067</t>
+          <t>2976; 13962</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>66924; 101108</t>
+          <t>68486; 103007</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>60753; 92272</t>
+          <t>60127; 94936</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28065; 51044</t>
+          <t>27479; 51455</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>80963; 123063</t>
+          <t>81875; 121034</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>72064; 112516</t>
+          <t>74511; 114013</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34149; 59297</t>
+          <t>33405; 59469</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6373; 23669</t>
+          <t>7248; 23635</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17211; 39190</t>
+          <t>17279; 39250</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1123; 10588</t>
+          <t>1247; 11652</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>28902; 53153</t>
+          <t>28958; 52852</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>41258; 70765</t>
+          <t>42662; 72747</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16434; 35566</t>
+          <t>15480; 35545</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40385; 69087</t>
+          <t>40887; 68933</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>63445; 102550</t>
+          <t>64839; 102939</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19640; 40022</t>
+          <t>20393; 40351</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>24075; 47433</t>
+          <t>23962; 46905</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23814; 47673</t>
+          <t>23968; 46043</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5672; 18177</t>
+          <t>5728; 18298</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>87708; 128580</t>
+          <t>86995; 126038</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>90781; 128624</t>
+          <t>88755; 128635</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28581; 54361</t>
+          <t>29073; 54826</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>118269; 163727</t>
+          <t>120586; 170734</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>118848; 164531</t>
+          <t>118316; 165591</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>37305; 65584</t>
+          <t>38213; 68418</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>49328; 82988</t>
+          <t>49932; 83563</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>67959; 106551</t>
+          <t>67604; 107270</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21737; 46443</t>
+          <t>22738; 44824</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>233817; 295437</t>
+          <t>234755; 298441</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>231049; 297812</t>
+          <t>231100; 295831</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>103962; 145822</t>
+          <t>105302; 147208</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>292503; 368021</t>
+          <t>295689; 368387</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>315059; 389265</t>
+          <t>312254; 388136</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>133144; 182921</t>
+          <t>134776; 182516</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Q45B_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/Q45B_R-Habitat-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,36</t>
+          <t>0,0; 1,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,54</t>
+          <t>0,77; 2,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,53</t>
+          <t>0,71; 2,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,43; 6,58</t>
+          <t>3,39; 6,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 5,07</t>
+          <t>2,19; 4,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,17; 4,7</t>
+          <t>2,15; 4,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,84; 3,45</t>
+          <t>1,82; 3,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,67; 3,37</t>
+          <t>1,68; 3,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,18</t>
+          <t>1,65; 3,31</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,69</t>
+          <t>1,02; 2,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,57</t>
+          <t>0,92; 2,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,32 +803,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,07; 10,64</t>
+          <t>6,95; 10,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,85; 9,24</t>
+          <t>5,81; 9,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,64; 4,94</t>
+          <t>2,67; 4,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,24; 6,27</t>
+          <t>4,3; 6,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,65; 5,59</t>
+          <t>3,55; 5,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,62; 2,89</t>
+          <t>1,66; 2,86</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 3,48</t>
+          <t>0,97; 3,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,29; 5,19</t>
+          <t>2,3; 5,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,54</t>
+          <t>0,15; 1,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,23; 7,73</t>
+          <t>4,35; 7,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,53; 9,42</t>
+          <t>5,55; 9,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,54</t>
+          <t>2,1; 4,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,0; 5,06</t>
+          <t>2,94; 5,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,24; 6,74</t>
+          <t>4,26; 6,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 2,62</t>
+          <t>1,25; 2,72</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,54; 4,98</t>
+          <t>2,49; 4,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,54; 4,87</t>
+          <t>2,47; 5,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,96</t>
+          <t>0,6; 1,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,38; 12,14</t>
+          <t>8,68; 12,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,46; 12,26</t>
+          <t>8,58; 12,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,8; 5,28</t>
+          <t>2,76; 5,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,09; 8,62</t>
+          <t>5,95; 8,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,93; 8,3</t>
+          <t>5,98; 8,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,94; 3,47</t>
+          <t>1,93; 3,34</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,55</t>
+          <t>1,52; 2,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,98; 3,14</t>
+          <t>2,04; 3,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 1,33</t>
+          <t>0,66; 1,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,95; 8,83</t>
+          <t>6,94; 8,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,52; 8,35</t>
+          <t>6,55; 8,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,98; 4,17</t>
+          <t>2,98; 4,14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,44; 5,53</t>
+          <t>4,39; 5,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,49; 5,58</t>
+          <t>4,52; 5,58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,95; 2,64</t>
+          <t>1,93; 2,63</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 9423</t>
+          <t>0; 10240</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5175; 17806</t>
+          <t>5421; 19131</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4932; 17084</t>
+          <t>4808; 17643</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23598; 45278</t>
+          <t>23336; 44486</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15572; 35281</t>
+          <t>15253; 34169</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14555; 31476</t>
+          <t>14362; 32504</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25417; 47655</t>
+          <t>25091; 47962</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>23338; 47135</t>
+          <t>23415; 47256</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>22122; 42708</t>
+          <t>22146; 44503</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9004; 25901</t>
+          <t>9801; 27625</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9122; 25965</t>
+          <t>9332; 27041</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2976; 13962</t>
+          <t>2985; 13866</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>68486; 103007</t>
+          <t>67299; 101029</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>60127; 94936</t>
+          <t>59681; 94784</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27479; 51455</t>
+          <t>27850; 51959</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>81875; 121034</t>
+          <t>83001; 122997</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>74511; 114013</t>
+          <t>72314; 110815</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>33405; 59469</t>
+          <t>34215; 58883</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7248; 23635</t>
+          <t>6550; 23730</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17279; 39250</t>
+          <t>17409; 39695</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1247; 11652</t>
+          <t>1115; 10546</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>28958; 52852</t>
+          <t>29734; 52733</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>42662; 72747</t>
+          <t>42848; 71512</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15480; 35545</t>
+          <t>16456; 35456</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40887; 68933</t>
+          <t>40100; 69454</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>64839; 102939</t>
+          <t>65020; 104417</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>20393; 40351</t>
+          <t>19281; 41883</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23962; 46905</t>
+          <t>23428; 46265</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23968; 46043</t>
+          <t>23368; 47518</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5728; 18298</t>
+          <t>5607; 17904</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>86995; 126038</t>
+          <t>90144; 130617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>88755; 128635</t>
+          <t>90048; 126635</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29073; 54826</t>
+          <t>28690; 54079</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>120586; 170734</t>
+          <t>117950; 165099</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>118316; 165591</t>
+          <t>119172; 163165</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>38213; 68418</t>
+          <t>38098; 65897</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>49932; 83563</t>
+          <t>49774; 82123</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>67604; 107270</t>
+          <t>69767; 106528</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22738; 44824</t>
+          <t>22425; 43031</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>234755; 298441</t>
+          <t>234665; 299743</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>231100; 295831</t>
+          <t>232067; 295192</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>105302; 147208</t>
+          <t>105092; 146124</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>295689; 368387</t>
+          <t>291859; 361735</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>312254; 388136</t>
+          <t>314296; 388280</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>134776; 182516</t>
+          <t>133241; 182052</t>
         </is>
       </c>
     </row>
